--- a/config/data/EventFilter.xlsx
+++ b/config/data/EventFilter.xlsx
@@ -497,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P8"/>
+  <dimension ref="A1:P10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.7109375" customWidth="1" min="1" max="1"/>
@@ -959,6 +959,47 @@
         </is>
       </c>
       <c r="P8" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="n">
+        <v>980545</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s01.filter.maple-retaliation</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>980402</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="n">
+        <v>980542</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s01.filter.synwood-renewal-owner-turn</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>980402</v>
+      </c>
+      <c r="P10" t="inlineStr">
         <is>
           <t>Any</t>
         </is>

--- a/config/data/EventFilter.xlsx
+++ b/config/data/EventFilter.xlsx
@@ -497,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P10"/>
+  <dimension ref="A1:P11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.7109375" customWidth="1" min="1" max="1"/>
@@ -1000,6 +1000,24 @@
         <v>980402</v>
       </c>
       <c r="P10" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="n">
+        <v>1010542</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s04.filter.weakness-break-owner</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>1010402</v>
+      </c>
+      <c r="P11" t="inlineStr">
         <is>
           <t>Any</t>
         </is>

--- a/config/data/EventFilter.xlsx
+++ b/config/data/EventFilter.xlsx
@@ -497,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P11"/>
+  <dimension ref="A1:P16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.7109375" customWidth="1" min="1" max="1"/>
@@ -1018,6 +1018,101 @@
         <v>1010402</v>
       </c>
       <c r="P11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="n">
+        <v>1020555</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s05.filter.ordeal-freeze</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>1020402</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Summon</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="n">
+        <v>1020551</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s05.filter.core-wind-break</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>1020402</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="n">
+        <v>1020552</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s05.filter.core-lightning-break</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>1020402</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="n">
+        <v>1020553</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s05.filter.core-imaginary-break</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>1020402</v>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="n">
+        <v>1020554</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s05.filter.formation-collapse</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>1020417</v>
+      </c>
+      <c r="P16" t="inlineStr">
         <is>
           <t>Any</t>
         </is>

--- a/config/data/EventFilter.xlsx
+++ b/config/data/EventFilter.xlsx
@@ -497,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P16"/>
+  <dimension ref="A1:P18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.7109375" customWidth="1" min="1" max="1"/>
@@ -1113,6 +1113,64 @@
         <v>1020417</v>
       </c>
       <c r="P16" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="n">
+        <v>1030551</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s06.filter.freeze-applied</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>1030501</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Effect</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>1030402</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1030414</v>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="n">
+        <v>1030552</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s06.filter.freeze-removed</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>1030501</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Effect</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>1030402</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1030414</v>
+      </c>
+      <c r="P18" t="inlineStr">
         <is>
           <t>Any</t>
         </is>

--- a/config/data/EventFilter.xlsx
+++ b/config/data/EventFilter.xlsx
@@ -497,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P18"/>
+  <dimension ref="A1:P19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.7109375" customWidth="1" min="1" max="1"/>
@@ -1171,6 +1171,29 @@
         <v>1030414</v>
       </c>
       <c r="P18" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="n">
+        <v>1040551</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s07.filter.tit-for-tat</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>1040402</v>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
         <is>
           <t>Any</t>
         </is>

--- a/config/data/EventFilter.xlsx
+++ b/config/data/EventFilter.xlsx
@@ -497,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P19"/>
+  <dimension ref="A1:P20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.7109375" customWidth="1" min="1" max="1"/>
@@ -1194,6 +1194,24 @@
         </is>
       </c>
       <c r="P19" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="n">
+        <v>1050542</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s08.filter.weakness-break-owner</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>1050402</v>
+      </c>
+      <c r="P20" t="inlineStr">
         <is>
           <t>Any</t>
         </is>

--- a/config/data/EventFilter.xlsx
+++ b/config/data/EventFilter.xlsx
@@ -497,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P20"/>
+  <dimension ref="A1:P29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.7109375" customWidth="1" min="1" max="1"/>
@@ -1212,6 +1212,168 @@
         <v>1050402</v>
       </c>
       <c r="P20" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="n">
+        <v>1060641</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s09.filter.sunset-actions</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>1060406</v>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="n">
+        <v>1060643</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s09.filter.nightfall-actions</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>1060406</v>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="n">
+        <v>1060642</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s09.filter.sunset-break</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>1060402</v>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="n">
+        <v>1060644</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s09.filter.nightfall-break</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>1060402</v>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="n">
+        <v>1060645</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s09.filter.tomb-bars</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>1060402</v>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="n">
+        <v>1060646</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s09.filter.tomb-release-0</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>1060402</v>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="n">
+        <v>1060647</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s09.filter.tomb-release-1</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>1060402</v>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="n">
+        <v>1060648</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s09.filter.tomb-release-2</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>1060402</v>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="n">
+        <v>1060649</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s09.filter.tomb-release-3</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>1060402</v>
+      </c>
+      <c r="P29" t="inlineStr">
         <is>
           <t>Any</t>
         </is>

--- a/config/data/EventFilter.xlsx
+++ b/config/data/EventFilter.xlsx
@@ -497,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P29"/>
+  <dimension ref="A1:P30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.7109375" customWidth="1" min="1" max="1"/>
@@ -1376,6 +1376,27 @@
       <c r="P29" t="inlineStr">
         <is>
           <t>Any</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="n">
+        <v>1070641</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s10.filter.cruelty</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>1070411</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1070410</v>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>RootCommand</t>
         </is>
       </c>
     </row>

--- a/config/data/EventFilter.xlsx
+++ b/config/data/EventFilter.xlsx
@@ -497,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P30"/>
+  <dimension ref="A1:P31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.7109375" customWidth="1" min="1" max="1"/>
@@ -1397,6 +1397,24 @@
       <c r="P30" t="inlineStr">
         <is>
           <t>RootCommand</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="n">
+        <v>1095102</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s12.filter.golden-hound-defeated</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>1090402</v>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Any</t>
         </is>
       </c>
     </row>

--- a/config/data/EventFilter.xlsx
+++ b/config/data/EventFilter.xlsx
@@ -497,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P31"/>
+  <dimension ref="A1:P32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.7109375" customWidth="1" min="1" max="1"/>
@@ -1413,6 +1413,24 @@
         <v>1090402</v>
       </c>
       <c r="P31" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="n">
+        <v>1105102</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s13.filter.automaton-spider-chains-defeated</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>1100402</v>
+      </c>
+      <c r="P32" t="inlineStr">
         <is>
           <t>Any</t>
         </is>

--- a/config/data/EventFilter.xlsx
+++ b/config/data/EventFilter.xlsx
@@ -497,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P32"/>
+  <dimension ref="A1:P33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.7109375" customWidth="1" min="1" max="1"/>
@@ -1431,6 +1431,24 @@
         <v>1100402</v>
       </c>
       <c r="P32" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="n">
+        <v>1115102</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s14.filter.illumination-dragonfish-candle-flame-defeated</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>1110402</v>
+      </c>
+      <c r="P33" t="inlineStr">
         <is>
           <t>Any</t>
         </is>

--- a/config/data/EventFilter.xlsx
+++ b/config/data/EventFilter.xlsx
@@ -497,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P33"/>
+  <dimension ref="A1:P34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.7109375" customWidth="1" min="1" max="1"/>
@@ -1449,6 +1449,24 @@
         <v>1110402</v>
       </c>
       <c r="P33" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="n">
+        <v>1125102</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s15.filter.mara-struck-soldier-rebirth-defeated</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>1120402</v>
+      </c>
+      <c r="P34" t="inlineStr">
         <is>
           <t>Any</t>
         </is>

--- a/config/data/EventFilter.xlsx
+++ b/config/data/EventFilter.xlsx
@@ -497,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P34"/>
+  <dimension ref="A1:P35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.7109375" customWidth="1" min="1" max="1"/>
@@ -1467,6 +1467,24 @@
         <v>1120402</v>
       </c>
       <c r="P34" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="n">
+        <v>1135102</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s16.filter.silvermane-lieutenant-shield-reflect-defeated</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
+        <v>1130402</v>
+      </c>
+      <c r="P35" t="inlineStr">
         <is>
           <t>Any</t>
         </is>

--- a/config/data/EventFilter.xlsx
+++ b/config/data/EventFilter.xlsx
@@ -497,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P35"/>
+  <dimension ref="A1:P36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.7109375" customWidth="1" min="1" max="1"/>
@@ -1485,6 +1485,24 @@
         <v>1130402</v>
       </c>
       <c r="P35" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="n">
+        <v>1145102</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s17.filter.voidranger-eliminator-detonated-defeated</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>1140402</v>
+      </c>
+      <c r="P36" t="inlineStr">
         <is>
           <t>Any</t>
         </is>

--- a/config/data/EventFilter.xlsx
+++ b/config/data/EventFilter.xlsx
@@ -497,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P8"/>
+  <dimension ref="A1:P36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.7109375" customWidth="1" min="1" max="1"/>
@@ -959,6 +959,550 @@
         </is>
       </c>
       <c r="P8" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="n">
+        <v>980545</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s01.filter.maple-retaliation</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>980402</v>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="n">
+        <v>980542</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s01.filter.synwood-renewal-owner-turn</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>980402</v>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="n">
+        <v>1010542</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s04.filter.weakness-break-owner</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>1010402</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="n">
+        <v>1020555</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s05.filter.ordeal-freeze</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>1020402</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Summon</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="n">
+        <v>1020551</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s05.filter.core-wind-break</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>1020402</v>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="n">
+        <v>1020552</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s05.filter.core-lightning-break</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>1020402</v>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="n">
+        <v>1020553</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s05.filter.core-imaginary-break</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>1020402</v>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="n">
+        <v>1020554</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s05.filter.formation-collapse</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>1020417</v>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="n">
+        <v>1030551</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s06.filter.freeze-applied</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>1030501</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Effect</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
+        <v>1030402</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1030414</v>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="n">
+        <v>1030552</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s06.filter.freeze-removed</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>1030501</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Effect</t>
+        </is>
+      </c>
+      <c r="F18" t="n">
+        <v>1030402</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1030414</v>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="n">
+        <v>1040551</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s07.filter.tit-for-tat</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>1040402</v>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="n">
+        <v>1050542</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s08.filter.weakness-break-owner</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>1050402</v>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="n">
+        <v>1060641</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s09.filter.sunset-actions</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>1060406</v>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="n">
+        <v>1060643</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s09.filter.nightfall-actions</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>1060406</v>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="n">
+        <v>1060642</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s09.filter.sunset-break</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>1060402</v>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="n">
+        <v>1060644</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s09.filter.nightfall-break</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>1060402</v>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="n">
+        <v>1060645</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s09.filter.tomb-bars</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>1060402</v>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" t="n">
+        <v>1060646</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s09.filter.tomb-release-0</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>1060402</v>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="n">
+        <v>1060647</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s09.filter.tomb-release-1</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>1060402</v>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" t="n">
+        <v>1060648</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s09.filter.tomb-release-2</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>1060402</v>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="n">
+        <v>1060649</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s09.filter.tomb-release-3</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>1060402</v>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="n">
+        <v>1070641</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s10.filter.cruelty</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>1070411</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1070410</v>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>RootCommand</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" t="n">
+        <v>1095102</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s12.filter.golden-hound-defeated</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>1090402</v>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="n">
+        <v>1105102</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s13.filter.automaton-spider-chains-defeated</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>1100402</v>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" t="n">
+        <v>1115102</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s14.filter.illumination-dragonfish-candle-flame-defeated</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>1110402</v>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="n">
+        <v>1125102</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s15.filter.mara-struck-soldier-rebirth-defeated</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>1120402</v>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="n">
+        <v>1135102</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s16.filter.silvermane-lieutenant-shield-reflect-defeated</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
+        <v>1130402</v>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="n">
+        <v>1145102</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>goal07.enemy.s17.filter.voidranger-eliminator-detonated-defeated</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>1140402</v>
+      </c>
+      <c r="P36" t="inlineStr">
         <is>
           <t>Any</t>
         </is>

--- a/config/data/EventFilter.xlsx
+++ b/config/data/EventFilter.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="EventFilter" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EventFilter" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -546,12 +546,12 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>@scope</t>
+          <t>@groups</t>
         </is>
       </c>
       <c r="H1" s="2" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>common</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -561,7 +561,7 @@
       </c>
       <c r="J1" s="2" t="inlineStr">
         <is>
-          <t>647b6f13916c7a3d</t>
+          <t>05cad19c4156d2d7</t>
         </is>
       </c>
     </row>
@@ -814,82 +814,82 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>#scope</t>
+          <t>#groups</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>common</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>common</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>common</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>common</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>common</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>common</t>
         </is>
       </c>
       <c r="H5" s="5" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>common</t>
         </is>
       </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>common</t>
         </is>
       </c>
       <c r="J5" s="5" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>common</t>
         </is>
       </c>
       <c r="K5" s="5" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>common</t>
         </is>
       </c>
       <c r="L5" s="5" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>common</t>
         </is>
       </c>
       <c r="M5" s="5" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>common</t>
         </is>
       </c>
       <c r="N5" s="5" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>common</t>
         </is>
       </c>
       <c r="O5" s="5" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>common</t>
         </is>
       </c>
       <c r="P5" s="5" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>common</t>
         </is>
       </c>
     </row>
@@ -950,8 +950,10 @@
       <c r="P7" s="6" t="n"/>
     </row>
     <row r="8">
-      <c r="B8" t="n">
-        <v>24201</v>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>24201</t>
+        </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -965,16 +967,20 @@
       </c>
     </row>
     <row r="9">
-      <c r="B9" t="n">
-        <v>980545</v>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>980545</t>
+        </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
           <t>goal07.enemy.s01.filter.maple-retaliation</t>
         </is>
       </c>
-      <c r="I9" t="n">
-        <v>980402</v>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>980402</t>
+        </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -988,16 +994,20 @@
       </c>
     </row>
     <row r="10">
-      <c r="B10" t="n">
-        <v>980542</v>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>980542</t>
+        </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
           <t>goal07.enemy.s01.filter.synwood-renewal-owner-turn</t>
         </is>
       </c>
-      <c r="F10" t="n">
-        <v>980402</v>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>980402</t>
+        </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
@@ -1006,16 +1016,20 @@
       </c>
     </row>
     <row r="11">
-      <c r="B11" t="n">
-        <v>1010542</v>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>1010542</t>
+        </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
           <t>goal07.enemy.s04.filter.weakness-break-owner</t>
         </is>
       </c>
-      <c r="I11" t="n">
-        <v>1010402</v>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1010402</t>
+        </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
@@ -1024,20 +1038,24 @@
       </c>
     </row>
     <row r="12">
-      <c r="B12" t="n">
-        <v>1020555</v>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>1040551</t>
+        </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>goal07.enemy.s05.filter.ordeal-freeze</t>
-        </is>
-      </c>
-      <c r="G12" t="n">
-        <v>1020402</v>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Summon</t>
+          <t>goal07.enemy.s07.filter.tit-for-tat</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1040402</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Ordinary</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1047,16 +1065,20 @@
       </c>
     </row>
     <row r="13">
-      <c r="B13" t="n">
-        <v>1020551</v>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>1050542</t>
+        </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>goal07.enemy.s05.filter.core-wind-break</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>1020402</v>
+          <t>goal07.enemy.s08.filter.weakness-break-owner</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1050402</t>
+        </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
@@ -1065,16 +1087,20 @@
       </c>
     </row>
     <row r="14">
-      <c r="B14" t="n">
-        <v>1020552</v>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>1060641</t>
+        </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>goal07.enemy.s05.filter.core-lightning-break</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>1020402</v>
+          <t>goal07.enemy.s09.filter.sunset-actions</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>1060406</t>
+        </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
@@ -1083,16 +1109,20 @@
       </c>
     </row>
     <row r="15">
-      <c r="B15" t="n">
-        <v>1020553</v>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>1060643</t>
+        </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>goal07.enemy.s05.filter.core-imaginary-break</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>1020402</v>
+          <t>goal07.enemy.s09.filter.nightfall-actions</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>1060406</t>
+        </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
@@ -1101,16 +1131,20 @@
       </c>
     </row>
     <row r="16">
-      <c r="B16" t="n">
-        <v>1020554</v>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>1060642</t>
+        </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>goal07.enemy.s05.filter.formation-collapse</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>1020417</v>
+          <t>goal07.enemy.s09.filter.sunset-break</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1060402</t>
+        </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
@@ -1119,27 +1153,20 @@
       </c>
     </row>
     <row r="17">
-      <c r="B17" t="n">
-        <v>1030551</v>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>1060644</t>
+        </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>goal07.enemy.s06.filter.freeze-applied</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>1030501</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Effect</t>
-        </is>
-      </c>
-      <c r="F17" t="n">
-        <v>1030402</v>
-      </c>
-      <c r="I17" t="n">
-        <v>1030414</v>
+          <t>goal07.enemy.s09.filter.nightfall-break</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1060402</t>
+        </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
@@ -1148,27 +1175,20 @@
       </c>
     </row>
     <row r="18">
-      <c r="B18" t="n">
-        <v>1030552</v>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>1060645</t>
+        </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>goal07.enemy.s06.filter.freeze-removed</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>1030501</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Effect</t>
-        </is>
-      </c>
-      <c r="F18" t="n">
-        <v>1030402</v>
-      </c>
-      <c r="I18" t="n">
-        <v>1030414</v>
+          <t>goal07.enemy.s09.filter.tomb-bars</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1060402</t>
+        </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
@@ -1177,20 +1197,19 @@
       </c>
     </row>
     <row r="19">
-      <c r="B19" t="n">
-        <v>1040551</v>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>1060646</t>
+        </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>goal07.enemy.s07.filter.tit-for-tat</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>1040402</v>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>Ordinary</t>
+          <t>goal07.enemy.s09.filter.tomb-release-0</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1060402</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -1200,16 +1219,20 @@
       </c>
     </row>
     <row r="20">
-      <c r="B20" t="n">
-        <v>1050542</v>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>1060647</t>
+        </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>goal07.enemy.s08.filter.weakness-break-owner</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>1050402</v>
+          <t>goal07.enemy.s09.filter.tomb-release-1</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1060402</t>
+        </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
@@ -1218,16 +1241,20 @@
       </c>
     </row>
     <row r="21">
-      <c r="B21" t="n">
-        <v>1060641</v>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>1060648</t>
+        </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>goal07.enemy.s09.filter.sunset-actions</t>
-        </is>
-      </c>
-      <c r="G21" t="n">
-        <v>1060406</v>
+          <t>goal07.enemy.s09.filter.tomb-release-2</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1060402</t>
+        </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
@@ -1236,16 +1263,20 @@
       </c>
     </row>
     <row r="22">
-      <c r="B22" t="n">
-        <v>1060643</v>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>1060649</t>
+        </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>goal07.enemy.s09.filter.nightfall-actions</t>
-        </is>
-      </c>
-      <c r="G22" t="n">
-        <v>1060406</v>
+          <t>goal07.enemy.s09.filter.tomb-release-3</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1060402</t>
+        </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
@@ -1254,34 +1285,47 @@
       </c>
     </row>
     <row r="23">
-      <c r="B23" t="n">
-        <v>1060642</v>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>1070641</t>
+        </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>goal07.enemy.s09.filter.sunset-break</t>
-        </is>
-      </c>
-      <c r="I23" t="n">
-        <v>1060402</v>
+          <t>goal07.enemy.s10.filter.cruelty</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>1070411</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1070410</t>
+        </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Any</t>
+          <t>RootCommand</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="B24" t="n">
-        <v>1060644</v>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>1095102</t>
+        </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>goal07.enemy.s09.filter.nightfall-break</t>
-        </is>
-      </c>
-      <c r="I24" t="n">
-        <v>1060402</v>
+          <t>goal07.enemy.s12.filter.golden-hound-defeated</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1090402</t>
+        </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
@@ -1290,16 +1334,20 @@
       </c>
     </row>
     <row r="25">
-      <c r="B25" t="n">
-        <v>1060645</v>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>1105102</t>
+        </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>goal07.enemy.s09.filter.tomb-bars</t>
-        </is>
-      </c>
-      <c r="I25" t="n">
-        <v>1060402</v>
+          <t>goal07.enemy.s13.filter.automaton-spider-chains-defeated</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1100402</t>
+        </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
@@ -1308,16 +1356,20 @@
       </c>
     </row>
     <row r="26">
-      <c r="B26" t="n">
-        <v>1060646</v>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>1115102</t>
+        </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>goal07.enemy.s09.filter.tomb-release-0</t>
-        </is>
-      </c>
-      <c r="I26" t="n">
-        <v>1060402</v>
+          <t>goal07.enemy.s14.filter.illumination-dragonfish-candle-flame-defeated</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1110402</t>
+        </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
@@ -1326,16 +1378,20 @@
       </c>
     </row>
     <row r="27">
-      <c r="B27" t="n">
-        <v>1060647</v>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>1125102</t>
+        </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>goal07.enemy.s09.filter.tomb-release-1</t>
-        </is>
-      </c>
-      <c r="I27" t="n">
-        <v>1060402</v>
+          <t>goal07.enemy.s15.filter.mara-struck-soldier-rebirth-defeated</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1120402</t>
+        </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
@@ -1344,16 +1400,20 @@
       </c>
     </row>
     <row r="28">
-      <c r="B28" t="n">
-        <v>1060648</v>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>1135102</t>
+        </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>goal07.enemy.s09.filter.tomb-release-2</t>
-        </is>
-      </c>
-      <c r="I28" t="n">
-        <v>1060402</v>
+          <t>goal07.enemy.s16.filter.silvermane-lieutenant-shield-reflect-defeated</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1130402</t>
+        </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
@@ -1363,15 +1423,20 @@
     </row>
     <row r="29">
       <c r="B29" t="n">
-        <v>1060649</v>
+        <v>1020555</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>goal07.enemy.s09.filter.tomb-release-3</t>
-        </is>
-      </c>
-      <c r="I29" t="n">
-        <v>1060402</v>
+          <t>goal07.enemy.s05.filter.ordeal-freeze</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>1020402</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Summon</t>
+        </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
@@ -1381,36 +1446,33 @@
     </row>
     <row r="30">
       <c r="B30" t="n">
-        <v>1070641</v>
+        <v>1020551</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>goal07.enemy.s10.filter.cruelty</t>
-        </is>
-      </c>
-      <c r="G30" t="n">
-        <v>1070411</v>
+          <t>goal07.enemy.s05.filter.core-wind-break</t>
+        </is>
       </c>
       <c r="I30" t="n">
-        <v>1070410</v>
+        <v>1020402</v>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>RootCommand</t>
+          <t>Any</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="B31" t="n">
-        <v>1095102</v>
+        <v>1020552</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>goal07.enemy.s12.filter.golden-hound-defeated</t>
+          <t>goal07.enemy.s05.filter.core-lightning-break</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1090402</v>
+        <v>1020402</v>
       </c>
       <c r="P31" t="inlineStr">
         <is>
@@ -1420,15 +1482,15 @@
     </row>
     <row r="32">
       <c r="B32" t="n">
-        <v>1105102</v>
+        <v>1020553</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>goal07.enemy.s13.filter.automaton-spider-chains-defeated</t>
+          <t>goal07.enemy.s05.filter.core-imaginary-break</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1100402</v>
+        <v>1020402</v>
       </c>
       <c r="P32" t="inlineStr">
         <is>
@@ -1438,15 +1500,15 @@
     </row>
     <row r="33">
       <c r="B33" t="n">
-        <v>1115102</v>
+        <v>1020554</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>goal07.enemy.s14.filter.illumination-dragonfish-candle-flame-defeated</t>
+          <t>goal07.enemy.s05.filter.formation-collapse</t>
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1110402</v>
+        <v>1020417</v>
       </c>
       <c r="P33" t="inlineStr">
         <is>
@@ -1456,15 +1518,15 @@
     </row>
     <row r="34">
       <c r="B34" t="n">
-        <v>1125102</v>
+        <v>1145102</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>goal07.enemy.s15.filter.mara-struck-soldier-rebirth-defeated</t>
+          <t>goal07.enemy.s17.filter.voidranger-eliminator-detonated-defeated</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1120402</v>
+        <v>1140402</v>
       </c>
       <c r="P34" t="inlineStr">
         <is>
@@ -1474,15 +1536,26 @@
     </row>
     <row r="35">
       <c r="B35" t="n">
-        <v>1135102</v>
+        <v>1030551</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>goal07.enemy.s16.filter.silvermane-lieutenant-shield-reflect-defeated</t>
-        </is>
+          <t>goal07.enemy.s06.filter.freeze-applied</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>1030501</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Effect</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>1030402</v>
       </c>
       <c r="I35" t="n">
-        <v>1130402</v>
+        <v>1030414</v>
       </c>
       <c r="P35" t="inlineStr">
         <is>
@@ -1492,15 +1565,26 @@
     </row>
     <row r="36">
       <c r="B36" t="n">
-        <v>1145102</v>
+        <v>1030552</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>goal07.enemy.s17.filter.voidranger-eliminator-detonated-defeated</t>
-        </is>
+          <t>goal07.enemy.s06.filter.freeze-removed</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>1030501</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Effect</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>1030402</v>
       </c>
       <c r="I36" t="n">
-        <v>1140402</v>
+        <v>1030414</v>
       </c>
       <c r="P36" t="inlineStr">
         <is>
